--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/20 13:53:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21700</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/20 11:57:32</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22988.51</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>22988.51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22988</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21700.51</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.51</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 11:57:21</t>
+          <t>09/29 10:26:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22988.51</t>
+          <t>19393.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/20 13:53:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21700</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 11:57:32</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19393.94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22988.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22988</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.51</t>
+          <t>19393.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/29 13:05:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19393</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19393.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19393</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19393.94</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 10:26:41</t>
+          <t>09/30 10:13:10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>36144.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/29 13:05:36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>19393</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19393.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19393</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/30 11:43:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36144.58</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36144</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>36144.58</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.58</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 10:13:10</t>
+          <t>10/13 11:17:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/30 11:43:43</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>36144</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>36144.58</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36144</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.58</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/13 11:17:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11476.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/13 13:53:23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11476</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/13 11:17:38</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11476.71</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 11:17:28</t>
+          <t>10/14 10:49:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>26666.67</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/13 13:53:23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11476</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/13 11:17:38</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>26666.67</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>26666.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/14 14:16:41</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>26666</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26666.67</t>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26666.67</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26666</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>26666.67</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/14 10:49:06</t>
+          <t>10/18 16:40:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26666.67</t>
+          <t>4344.37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/14 14:16:41</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>26666</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>37796</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>4344.37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26666.67</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26666</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.67</t>
+          <t>4344.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/18 17:45:20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>37796</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4344.37</t>
+          <t>37796</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4344.37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>4344.37</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.37</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 16:40:32</t>
+          <t>10/26 11:51:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37796</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4344.37</t>
+          <t>17682.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/18 17:45:20</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4344</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37796</t>
+          <t>17682.93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4344.37</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4344</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.37</t>
+          <t>17682.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/26 13:32:24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17682</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>145000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17682.93</t>
+          <t>145000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17682.93</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17682</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17682.93</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.93</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:51:28</t>
+          <t>10/27 17:41:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17682.93</t>
+          <t>13253.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/26 13:32:24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>17682</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>13253.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17682.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17682</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.93</t>
+          <t>13253.01</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
+++ b/bills/JXZFSP01/-1003524424809/9e01c3be2903652029e0afbd7efea6ab6e62092ce14bf7ce603bf21aa9a5ca2e/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/27 19:06:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>110000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13253.01</t>
+          <t>110000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13253.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>13253.01</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
